--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wysha_Object\wysha_Project\WebProjects\TypeWords\apps\nuxt\i18n\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB7D4BC-824B-407B-8236-16AECD6180B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView xWindow="-105" yWindow="-16200" windowWidth="29010" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7710" uniqueCount="7165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7830" uniqueCount="7181">
   <si>
     <t>key</t>
   </si>
@@ -21536,19 +21542,77 @@
   </si>
   <si>
     <t>开启后，将使用FSRS算法来决定需要复习的单词,而非固定单词数量</t>
+  </si>
+  <si>
+    <t>fsrs_settings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FSRS设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_easy_limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_good_limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_hard_limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Easy评级判定标准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Good评级判定标准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hard评级判定标准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_limit_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>less_or_equals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>times</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wrong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小于等于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在单次学习的整个过程中每个单词的错误次数会被用以给其评级,共有四个评级,Again,Hard,Good,Easy,FSRS算法会使用评级来计算这个单词下一次需要复习的时间,启用或禁用FSRS仅影响生成复习词的规则,不影响上述过程的执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -21557,352 +21621,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -21910,311 +21652,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -22536,20 +21995,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O514"/>
-  <sheetFormatPr defaultColWidth="9.64166666666667" defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O522"/>
+  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="37.4166666666667" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="21.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22596,7 +22055,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -22643,7 +22102,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -22690,7 +22149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -22737,7 +22196,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -22784,7 +22243,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -22831,7 +22290,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -22878,7 +22337,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -22925,7 +22384,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -22972,7 +22431,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -23019,7 +22478,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -23066,7 +22525,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -23113,7 +22572,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -23160,7 +22619,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -23207,7 +22666,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>195</v>
       </c>
@@ -23254,7 +22713,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>210</v>
       </c>
@@ -23301,7 +22760,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>225</v>
       </c>
@@ -23348,7 +22807,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>240</v>
       </c>
@@ -23395,7 +22854,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>255</v>
       </c>
@@ -23442,7 +22901,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>270</v>
       </c>
@@ -23489,7 +22948,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>285</v>
       </c>
@@ -23536,7 +22995,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>300</v>
       </c>
@@ -23583,7 +23042,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>314</v>
       </c>
@@ -23630,7 +23089,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>328</v>
       </c>
@@ -23677,7 +23136,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>342</v>
       </c>
@@ -23724,7 +23183,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>357</v>
       </c>
@@ -23771,7 +23230,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>372</v>
       </c>
@@ -23818,7 +23277,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>387</v>
       </c>
@@ -23865,7 +23324,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>402</v>
       </c>
@@ -23912,7 +23371,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>417</v>
       </c>
@@ -23959,7 +23418,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>432</v>
       </c>
@@ -24006,7 +23465,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>447</v>
       </c>
@@ -24053,7 +23512,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>462</v>
       </c>
@@ -24100,7 +23559,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>477</v>
       </c>
@@ -24147,7 +23606,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>492</v>
       </c>
@@ -24194,7 +23653,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>507</v>
       </c>
@@ -24241,7 +23700,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>510</v>
       </c>
@@ -24288,7 +23747,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>513</v>
       </c>
@@ -24335,7 +23794,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>528</v>
       </c>
@@ -24382,7 +23841,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>541</v>
       </c>
@@ -24429,7 +23888,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>556</v>
       </c>
@@ -24476,7 +23935,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>569</v>
       </c>
@@ -24523,7 +23982,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>582</v>
       </c>
@@ -24570,7 +24029,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>595</v>
       </c>
@@ -24617,7 +24076,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>610</v>
       </c>
@@ -24664,7 +24123,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>624</v>
       </c>
@@ -24711,7 +24170,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>638</v>
       </c>
@@ -24758,7 +24217,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>653</v>
       </c>
@@ -24805,7 +24264,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>667</v>
       </c>
@@ -24852,7 +24311,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>681</v>
       </c>
@@ -24899,7 +24358,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>694</v>
       </c>
@@ -24946,7 +24405,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>706</v>
       </c>
@@ -24993,7 +24452,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>719</v>
       </c>
@@ -25040,7 +24499,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>732</v>
       </c>
@@ -25087,7 +24546,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>747</v>
       </c>
@@ -25134,7 +24593,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>760</v>
       </c>
@@ -25181,7 +24640,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>775</v>
       </c>
@@ -25228,7 +24687,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>790</v>
       </c>
@@ -25275,7 +24734,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>805</v>
       </c>
@@ -25322,7 +24781,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>820</v>
       </c>
@@ -25369,7 +24828,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>835</v>
       </c>
@@ -25416,7 +24875,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>850</v>
       </c>
@@ -25463,7 +24922,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>865</v>
       </c>
@@ -25510,7 +24969,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>880</v>
       </c>
@@ -25557,7 +25016,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>895</v>
       </c>
@@ -25604,7 +25063,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>910</v>
       </c>
@@ -25651,7 +25110,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>925</v>
       </c>
@@ -25698,7 +25157,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>940</v>
       </c>
@@ -25745,7 +25204,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>955</v>
       </c>
@@ -25792,7 +25251,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>970</v>
       </c>
@@ -25839,7 +25298,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>985</v>
       </c>
@@ -25886,7 +25345,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>1000</v>
       </c>
@@ -25933,7 +25392,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>1015</v>
       </c>
@@ -25980,7 +25439,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>1030</v>
       </c>
@@ -26027,7 +25486,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>1045</v>
       </c>
@@ -26074,7 +25533,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>1060</v>
       </c>
@@ -26121,7 +25580,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>1075</v>
       </c>
@@ -26168,7 +25627,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>1090</v>
       </c>
@@ -26215,7 +25674,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
         <v>1105</v>
       </c>
@@ -26262,7 +25721,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
         <v>1120</v>
       </c>
@@ -26309,7 +25768,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>1135</v>
       </c>
@@ -26356,7 +25815,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>1149</v>
       </c>
@@ -26403,7 +25862,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
         <v>1162</v>
       </c>
@@ -26450,7 +25909,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
         <v>1173</v>
       </c>
@@ -26497,7 +25956,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
         <v>1188</v>
       </c>
@@ -26544,7 +26003,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
         <v>1202</v>
       </c>
@@ -26591,7 +26050,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
         <v>1217</v>
       </c>
@@ -26638,7 +26097,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>1232</v>
       </c>
@@ -26685,7 +26144,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
         <v>1247</v>
       </c>
@@ -26732,7 +26191,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
         <v>1262</v>
       </c>
@@ -26779,7 +26238,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>1277</v>
       </c>
@@ -26826,7 +26285,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
         <v>1292</v>
       </c>
@@ -26873,7 +26332,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="93" spans="1:15">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>1307</v>
       </c>
@@ -26920,7 +26379,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="94" spans="1:15">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>1321</v>
       </c>
@@ -26967,7 +26426,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
         <v>1336</v>
       </c>
@@ -27014,7 +26473,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="96" spans="1:15">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>1351</v>
       </c>
@@ -27061,7 +26520,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
         <v>1366</v>
       </c>
@@ -27108,7 +26567,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>1381</v>
       </c>
@@ -27155,7 +26614,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
         <v>1396</v>
       </c>
@@ -27202,7 +26661,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
         <v>1411</v>
       </c>
@@ -27249,7 +26708,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
         <v>1426</v>
       </c>
@@ -27296,7 +26755,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
         <v>1441</v>
       </c>
@@ -27343,7 +26802,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
         <v>1456</v>
       </c>
@@ -27390,7 +26849,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
         <v>1470</v>
       </c>
@@ -27437,7 +26896,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
         <v>1485</v>
       </c>
@@ -27484,7 +26943,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
         <v>1500</v>
       </c>
@@ -27531,7 +26990,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
         <v>1515</v>
       </c>
@@ -27578,7 +27037,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
         <v>1530</v>
       </c>
@@ -27625,7 +27084,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
         <v>1545</v>
       </c>
@@ -27672,7 +27131,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
         <v>1560</v>
       </c>
@@ -27719,7 +27178,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
         <v>1574</v>
       </c>
@@ -27766,7 +27225,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
         <v>1589</v>
       </c>
@@ -27813,7 +27272,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="113" spans="1:15">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
         <v>1604</v>
       </c>
@@ -27860,7 +27319,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
         <v>1619</v>
       </c>
@@ -27907,7 +27366,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
         <v>1634</v>
       </c>
@@ -27954,7 +27413,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="116" spans="1:15">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
         <v>1649</v>
       </c>
@@ -28001,7 +27460,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="117" spans="1:15">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
         <v>1660</v>
       </c>
@@ -28048,7 +27507,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="118" spans="1:15">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
         <v>1673</v>
       </c>
@@ -28095,7 +27554,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="119" spans="1:15">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
         <v>1688</v>
       </c>
@@ -28142,7 +27601,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="120" spans="1:15">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
         <v>1702</v>
       </c>
@@ -28189,7 +27648,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="121" spans="1:15">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
         <v>1715</v>
       </c>
@@ -28236,7 +27695,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="122" spans="1:15">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
         <v>1730</v>
       </c>
@@ -28283,7 +27742,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="123" spans="1:15">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
         <v>1745</v>
       </c>
@@ -28330,7 +27789,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="124" spans="1:15">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>1759</v>
       </c>
@@ -28377,7 +27836,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="125" spans="1:15">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>1774</v>
       </c>
@@ -28424,7 +27883,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="126" spans="1:15">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
         <v>1789</v>
       </c>
@@ -28471,7 +27930,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="127" spans="1:15">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
         <v>1804</v>
       </c>
@@ -28518,7 +27977,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="128" spans="1:15">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
         <v>1819</v>
       </c>
@@ -28565,7 +28024,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="129" spans="1:15">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A129" t="s">
         <v>1834</v>
       </c>
@@ -28612,7 +28071,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="130" spans="1:15">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A130" t="s">
         <v>1849</v>
       </c>
@@ -28659,7 +28118,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="131" spans="1:15">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A131" t="s">
         <v>1864</v>
       </c>
@@ -28706,7 +28165,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="132" spans="1:15">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A132" t="s">
         <v>1877</v>
       </c>
@@ -28753,7 +28212,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="133" spans="1:15">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
         <v>1889</v>
       </c>
@@ -28800,7 +28259,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="134" spans="1:15">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
         <v>1904</v>
       </c>
@@ -28847,7 +28306,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="135" spans="1:15">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A135" t="s">
         <v>1909</v>
       </c>
@@ -28894,7 +28353,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="136" spans="1:15">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
         <v>1924</v>
       </c>
@@ -28941,7 +28400,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="137" spans="1:15">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A137" t="s">
         <v>1939</v>
       </c>
@@ -28988,7 +28447,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="138" spans="1:15">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A138" t="s">
         <v>1954</v>
       </c>
@@ -29035,7 +28494,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="139" spans="1:15">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A139" t="s">
         <v>1969</v>
       </c>
@@ -29082,7 +28541,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="140" spans="1:15">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A140" t="s">
         <v>1984</v>
       </c>
@@ -29129,7 +28588,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="141" spans="1:15">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A141" t="s">
         <v>1999</v>
       </c>
@@ -29176,7 +28635,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="142" spans="1:15">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A142" t="s">
         <v>2013</v>
       </c>
@@ -29223,7 +28682,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="143" spans="1:15">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A143" t="s">
         <v>2028</v>
       </c>
@@ -29270,7 +28729,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="144" spans="1:15">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A144" t="s">
         <v>2043</v>
       </c>
@@ -29317,7 +28776,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="145" spans="1:15">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A145" t="s">
         <v>2058</v>
       </c>
@@ -29364,7 +28823,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="146" spans="1:15">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A146" t="s">
         <v>2073</v>
       </c>
@@ -29411,7 +28870,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="147" spans="1:15">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A147" t="s">
         <v>2088</v>
       </c>
@@ -29458,7 +28917,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="148" spans="1:15">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A148" t="s">
         <v>2102</v>
       </c>
@@ -29505,7 +28964,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="149" spans="1:15">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A149" t="s">
         <v>2117</v>
       </c>
@@ -29552,7 +29011,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="150" spans="1:15">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A150" t="s">
         <v>2132</v>
       </c>
@@ -29599,7 +29058,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A151" t="s">
         <v>2147</v>
       </c>
@@ -29646,7 +29105,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="152" spans="1:15">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A152" t="s">
         <v>2162</v>
       </c>
@@ -29693,7 +29152,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="153" spans="1:15">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A153" t="s">
         <v>2177</v>
       </c>
@@ -29740,7 +29199,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="154" spans="1:15">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A154" t="s">
         <v>2191</v>
       </c>
@@ -29787,7 +29246,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="155" spans="1:15">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A155" t="s">
         <v>2197</v>
       </c>
@@ -29834,7 +29293,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="156" spans="1:15">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A156" t="s">
         <v>2210</v>
       </c>
@@ -29881,7 +29340,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="157" spans="1:15">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A157" t="s">
         <v>2225</v>
       </c>
@@ -29928,7 +29387,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="158" spans="1:15">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A158" t="s">
         <v>2239</v>
       </c>
@@ -29975,7 +29434,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="159" spans="1:15">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A159" t="s">
         <v>2250</v>
       </c>
@@ -30022,7 +29481,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="160" spans="1:15">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A160" t="s">
         <v>2264</v>
       </c>
@@ -30069,7 +29528,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A161" t="s">
         <v>2279</v>
       </c>
@@ -30116,7 +29575,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="162" spans="1:15">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A162" t="s">
         <v>2294</v>
       </c>
@@ -30163,7 +29622,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A163" t="s">
         <v>2309</v>
       </c>
@@ -30210,7 +29669,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A164" t="s">
         <v>2324</v>
       </c>
@@ -30257,7 +29716,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="165" spans="1:15">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A165" t="s">
         <v>2339</v>
       </c>
@@ -30304,7 +29763,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="166" spans="1:15">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A166" t="s">
         <v>2354</v>
       </c>
@@ -30351,7 +29810,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="167" spans="1:15">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A167" t="s">
         <v>2368</v>
       </c>
@@ -30398,7 +29857,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="168" spans="1:15">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A168" t="s">
         <v>2382</v>
       </c>
@@ -30445,7 +29904,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A169" t="s">
         <v>2394</v>
       </c>
@@ -30492,7 +29951,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="170" spans="1:15">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A170" t="s">
         <v>2409</v>
       </c>
@@ -30539,7 +29998,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="171" spans="1:15">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A171" t="s">
         <v>2424</v>
       </c>
@@ -30586,7 +30045,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="172" spans="1:15">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A172" t="s">
         <v>2439</v>
       </c>
@@ -30633,7 +30092,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="173" spans="1:15">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A173" t="s">
         <v>2454</v>
       </c>
@@ -30680,7 +30139,7 @@
         <v>2468</v>
       </c>
     </row>
-    <row r="174" spans="1:15">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A174" t="s">
         <v>2469</v>
       </c>
@@ -30727,7 +30186,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="175" spans="1:15">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A175" t="s">
         <v>2481</v>
       </c>
@@ -30774,7 +30233,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="176" spans="1:15">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A176" t="s">
         <v>2494</v>
       </c>
@@ -30821,7 +30280,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="177" spans="1:15">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A177" t="s">
         <v>2509</v>
       </c>
@@ -30868,7 +30327,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="178" spans="1:15">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A178" t="s">
         <v>2524</v>
       </c>
@@ -30915,7 +30374,7 @@
         <v>2538</v>
       </c>
     </row>
-    <row r="179" spans="1:15">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A179" t="s">
         <v>2539</v>
       </c>
@@ -30962,7 +30421,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="180" spans="1:15">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A180" t="s">
         <v>2554</v>
       </c>
@@ -31009,7 +30468,7 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="181" spans="1:15">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A181" t="s">
         <v>2569</v>
       </c>
@@ -31056,7 +30515,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="182" spans="1:15">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A182" t="s">
         <v>2583</v>
       </c>
@@ -31103,7 +30562,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="183" spans="1:15">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A183" t="s">
         <v>2598</v>
       </c>
@@ -31150,7 +30609,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="184" spans="1:15">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A184" t="s">
         <v>2612</v>
       </c>
@@ -31197,7 +30656,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="185" spans="1:15">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A185" t="s">
         <v>2624</v>
       </c>
@@ -31244,7 +30703,7 @@
         <v>2638</v>
       </c>
     </row>
-    <row r="186" spans="1:15">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A186" t="s">
         <v>2639</v>
       </c>
@@ -31291,7 +30750,7 @@
         <v>2653</v>
       </c>
     </row>
-    <row r="187" spans="1:15">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A187" t="s">
         <v>2654</v>
       </c>
@@ -31338,7 +30797,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="188" spans="1:15">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A188" t="s">
         <v>2669</v>
       </c>
@@ -31385,7 +30844,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="189" spans="1:15">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A189" t="s">
         <v>2684</v>
       </c>
@@ -31432,7 +30891,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="190" spans="1:15">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A190" t="s">
         <v>2699</v>
       </c>
@@ -31479,7 +30938,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="191" spans="1:15">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A191" t="s">
         <v>2714</v>
       </c>
@@ -31526,7 +30985,7 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="192" spans="1:15">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A192" t="s">
         <v>2729</v>
       </c>
@@ -31573,7 +31032,7 @@
         <v>2743</v>
       </c>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A193" t="s">
         <v>2744</v>
       </c>
@@ -31620,7 +31079,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A194" t="s">
         <v>2759</v>
       </c>
@@ -31667,7 +31126,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A195" t="s">
         <v>2773</v>
       </c>
@@ -31714,7 +31173,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A196" t="s">
         <v>2786</v>
       </c>
@@ -31761,7 +31220,7 @@
         <v>2787</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A197" t="s">
         <v>2798</v>
       </c>
@@ -31808,7 +31267,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A198" t="s">
         <v>2812</v>
       </c>
@@ -31855,7 +31314,7 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A199" t="s">
         <v>2826</v>
       </c>
@@ -31902,7 +31361,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A200" t="s">
         <v>2840</v>
       </c>
@@ -31949,7 +31408,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="201" spans="1:15">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A201" t="s">
         <v>2855</v>
       </c>
@@ -31996,7 +31455,7 @@
         <v>2856</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A202" t="s">
         <v>2859</v>
       </c>
@@ -32043,7 +31502,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="203" spans="1:15">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A203" t="s">
         <v>2873</v>
       </c>
@@ -32090,7 +31549,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="204" spans="1:15">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A204" t="s">
         <v>2888</v>
       </c>
@@ -32137,7 +31596,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="205" spans="1:15">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A205" t="s">
         <v>2902</v>
       </c>
@@ -32184,7 +31643,7 @@
         <v>2916</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A206" t="s">
         <v>2917</v>
       </c>
@@ -32231,7 +31690,7 @@
         <v>2931</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A207" t="s">
         <v>2932</v>
       </c>
@@ -32278,7 +31737,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A208" t="s">
         <v>2947</v>
       </c>
@@ -32325,7 +31784,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A209" t="s">
         <v>2962</v>
       </c>
@@ -32372,7 +31831,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A210" t="s">
         <v>2977</v>
       </c>
@@ -32419,7 +31878,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A211" t="s">
         <v>2988</v>
       </c>
@@ -32466,7 +31925,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A212" t="s">
         <v>3002</v>
       </c>
@@ -32513,7 +31972,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A213" t="s">
         <v>3016</v>
       </c>
@@ -32560,7 +32019,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A214" t="s">
         <v>3031</v>
       </c>
@@ -32607,7 +32066,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A215" t="s">
         <v>3044</v>
       </c>
@@ -32654,7 +32113,7 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A216" t="s">
         <v>3048</v>
       </c>
@@ -32701,7 +32160,7 @@
         <v>3062</v>
       </c>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A217" t="s">
         <v>3063</v>
       </c>
@@ -32748,7 +32207,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A218" t="s">
         <v>3067</v>
       </c>
@@ -32795,7 +32254,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A219" t="s">
         <v>3082</v>
       </c>
@@ -32842,7 +32301,7 @@
         <v>3083</v>
       </c>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A220" t="s">
         <v>3092</v>
       </c>
@@ -32889,7 +32348,7 @@
         <v>3106</v>
       </c>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A221" t="s">
         <v>3107</v>
       </c>
@@ -32936,7 +32395,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A222" t="s">
         <v>3121</v>
       </c>
@@ -32983,7 +32442,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A223" t="s">
         <v>3136</v>
       </c>
@@ -33030,7 +32489,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A224" t="s">
         <v>3151</v>
       </c>
@@ -33077,7 +32536,7 @@
         <v>3152</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A225" t="s">
         <v>3164</v>
       </c>
@@ -33124,7 +32583,7 @@
         <v>3178</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A226" t="s">
         <v>3179</v>
       </c>
@@ -33171,7 +32630,7 @@
         <v>3180</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A227" t="s">
         <v>3192</v>
       </c>
@@ -33218,7 +32677,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="228" spans="1:15">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A228" t="s">
         <v>3207</v>
       </c>
@@ -33265,7 +32724,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="229" spans="1:15">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A229" t="s">
         <v>3222</v>
       </c>
@@ -33312,7 +32771,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="230" spans="1:15">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A230" t="s">
         <v>3237</v>
       </c>
@@ -33359,7 +32818,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A231" t="s">
         <v>3251</v>
       </c>
@@ -33406,7 +32865,7 @@
         <v>3265</v>
       </c>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A232" t="s">
         <v>3266</v>
       </c>
@@ -33453,7 +32912,7 @@
         <v>3280</v>
       </c>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A233" t="s">
         <v>3281</v>
       </c>
@@ -33500,7 +32959,7 @@
         <v>3295</v>
       </c>
     </row>
-    <row r="234" spans="1:15">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A234" t="s">
         <v>3296</v>
       </c>
@@ -33547,7 +33006,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="235" spans="1:15">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A235" t="s">
         <v>3311</v>
       </c>
@@ -33594,7 +33053,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="236" spans="1:15">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A236" t="s">
         <v>3326</v>
       </c>
@@ -33641,7 +33100,7 @@
         <v>3340</v>
       </c>
     </row>
-    <row r="237" spans="1:15">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A237" t="s">
         <v>3341</v>
       </c>
@@ -33688,7 +33147,7 @@
         <v>3355</v>
       </c>
     </row>
-    <row r="238" spans="1:15">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A238" t="s">
         <v>3356</v>
       </c>
@@ -33735,7 +33194,7 @@
         <v>3370</v>
       </c>
     </row>
-    <row r="239" spans="1:15">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A239" t="s">
         <v>3371</v>
       </c>
@@ -33782,7 +33241,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="240" spans="1:15">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A240" t="s">
         <v>3385</v>
       </c>
@@ -33829,7 +33288,7 @@
         <v>3399</v>
       </c>
     </row>
-    <row r="241" spans="1:15">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A241" t="s">
         <v>3400</v>
       </c>
@@ -33876,7 +33335,7 @@
         <v>3414</v>
       </c>
     </row>
-    <row r="242" spans="1:15">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A242" t="s">
         <v>3415</v>
       </c>
@@ -33923,7 +33382,7 @@
         <v>3429</v>
       </c>
     </row>
-    <row r="243" spans="1:15">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A243" t="s">
         <v>3430</v>
       </c>
@@ -33970,7 +33429,7 @@
         <v>3431</v>
       </c>
     </row>
-    <row r="244" spans="1:15">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A244" t="s">
         <v>3443</v>
       </c>
@@ -34017,7 +33476,7 @@
         <v>3444</v>
       </c>
     </row>
-    <row r="245" spans="1:15">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A245" t="s">
         <v>3457</v>
       </c>
@@ -34064,7 +33523,7 @@
         <v>3471</v>
       </c>
     </row>
-    <row r="246" spans="1:15">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A246" t="s">
         <v>3472</v>
       </c>
@@ -34111,7 +33570,7 @@
         <v>3486</v>
       </c>
     </row>
-    <row r="247" spans="1:15">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A247" t="s">
         <v>3487</v>
       </c>
@@ -34158,7 +33617,7 @@
         <v>3488</v>
       </c>
     </row>
-    <row r="248" spans="1:15">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A248" t="s">
         <v>3497</v>
       </c>
@@ -34205,7 +33664,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="249" spans="1:15">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A249" t="s">
         <v>3512</v>
       </c>
@@ -34252,7 +33711,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="250" spans="1:15">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A250" t="s">
         <v>3527</v>
       </c>
@@ -34299,7 +33758,7 @@
         <v>3541</v>
       </c>
     </row>
-    <row r="251" spans="1:15">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A251" t="s">
         <v>3542</v>
       </c>
@@ -34346,7 +33805,7 @@
         <v>3556</v>
       </c>
     </row>
-    <row r="252" spans="1:15">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A252" t="s">
         <v>3557</v>
       </c>
@@ -34393,7 +33852,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="253" spans="1:15">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A253" t="s">
         <v>3572</v>
       </c>
@@ -34440,7 +33899,7 @@
         <v>3586</v>
       </c>
     </row>
-    <row r="254" spans="1:15">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A254" t="s">
         <v>3587</v>
       </c>
@@ -34487,7 +33946,7 @@
         <v>3601</v>
       </c>
     </row>
-    <row r="255" spans="1:15">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A255" t="s">
         <v>3602</v>
       </c>
@@ -34534,7 +33993,7 @@
         <v>3616</v>
       </c>
     </row>
-    <row r="256" spans="1:15">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A256" t="s">
         <v>3617</v>
       </c>
@@ -34581,7 +34040,7 @@
         <v>3618</v>
       </c>
     </row>
-    <row r="257" spans="1:15">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A257" t="s">
         <v>3631</v>
       </c>
@@ -34628,7 +34087,7 @@
         <v>3645</v>
       </c>
     </row>
-    <row r="258" spans="1:15">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A258" t="s">
         <v>3646</v>
       </c>
@@ -34675,7 +34134,7 @@
         <v>3660</v>
       </c>
     </row>
-    <row r="259" spans="1:15">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A259" t="s">
         <v>3661</v>
       </c>
@@ -34722,7 +34181,7 @@
         <v>3675</v>
       </c>
     </row>
-    <row r="260" spans="1:15">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A260" t="s">
         <v>3676</v>
       </c>
@@ -34769,7 +34228,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="261" spans="1:15">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A261" t="s">
         <v>3691</v>
       </c>
@@ -34816,7 +34275,7 @@
         <v>3705</v>
       </c>
     </row>
-    <row r="262" spans="1:15">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A262" t="s">
         <v>3706</v>
       </c>
@@ -34863,7 +34322,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="263" spans="1:15">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A263" t="s">
         <v>3721</v>
       </c>
@@ -34910,7 +34369,7 @@
         <v>3722</v>
       </c>
     </row>
-    <row r="264" spans="1:15">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A264" t="s">
         <v>3730</v>
       </c>
@@ -34957,7 +34416,7 @@
         <v>3744</v>
       </c>
     </row>
-    <row r="265" spans="1:15">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A265" t="s">
         <v>3745</v>
       </c>
@@ -35004,7 +34463,7 @@
         <v>3746</v>
       </c>
     </row>
-    <row r="266" spans="1:15">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A266" t="s">
         <v>3759</v>
       </c>
@@ -35051,7 +34510,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="267" spans="1:15">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A267" t="s">
         <v>3773</v>
       </c>
@@ -35098,7 +34557,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="268" spans="1:15">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A268" t="s">
         <v>3788</v>
       </c>
@@ -35145,7 +34604,7 @@
         <v>3802</v>
       </c>
     </row>
-    <row r="269" spans="1:15">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A269" t="s">
         <v>3803</v>
       </c>
@@ -35192,7 +34651,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="270" spans="1:15">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A270" t="s">
         <v>3804</v>
       </c>
@@ -35239,7 +34698,7 @@
         <v>3818</v>
       </c>
     </row>
-    <row r="271" spans="1:15">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A271" t="s">
         <v>3819</v>
       </c>
@@ -35286,7 +34745,7 @@
         <v>3833</v>
       </c>
     </row>
-    <row r="272" spans="1:15">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A272" t="s">
         <v>3834</v>
       </c>
@@ -35333,7 +34792,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="273" spans="1:15">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A273" t="s">
         <v>3844</v>
       </c>
@@ -35380,7 +34839,7 @@
         <v>3845</v>
       </c>
     </row>
-    <row r="274" spans="1:15">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A274" t="s">
         <v>3857</v>
       </c>
@@ -35427,7 +34886,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="275" spans="1:15">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A275" t="s">
         <v>3871</v>
       </c>
@@ -35474,7 +34933,7 @@
         <v>3872</v>
       </c>
     </row>
-    <row r="276" spans="1:15">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A276" t="s">
         <v>3885</v>
       </c>
@@ -35521,7 +34980,7 @@
         <v>3898</v>
       </c>
     </row>
-    <row r="277" spans="1:15">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A277" t="s">
         <v>3899</v>
       </c>
@@ -35568,7 +35027,7 @@
         <v>3902</v>
       </c>
     </row>
-    <row r="278" spans="1:15">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A278" t="s">
         <v>3903</v>
       </c>
@@ -35615,7 +35074,7 @@
         <v>3915</v>
       </c>
     </row>
-    <row r="279" spans="1:15">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A279" t="s">
         <v>3916</v>
       </c>
@@ -35662,7 +35121,7 @@
         <v>3930</v>
       </c>
     </row>
-    <row r="280" spans="1:15">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A280" t="s">
         <v>3931</v>
       </c>
@@ -35709,7 +35168,7 @@
         <v>3945</v>
       </c>
     </row>
-    <row r="281" spans="1:15">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A281" t="s">
         <v>3946</v>
       </c>
@@ -35756,7 +35215,7 @@
         <v>3960</v>
       </c>
     </row>
-    <row r="282" spans="1:15">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A282" t="s">
         <v>3961</v>
       </c>
@@ -35803,7 +35262,7 @@
         <v>3975</v>
       </c>
     </row>
-    <row r="283" spans="1:15">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A283" t="s">
         <v>3976</v>
       </c>
@@ -35850,7 +35309,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="284" spans="1:15">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A284" t="s">
         <v>3991</v>
       </c>
@@ -35897,7 +35356,7 @@
         <v>4005</v>
       </c>
     </row>
-    <row r="285" spans="1:15">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A285" t="s">
         <v>4006</v>
       </c>
@@ -35944,7 +35403,7 @@
         <v>4020</v>
       </c>
     </row>
-    <row r="286" spans="1:15">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A286" t="s">
         <v>4021</v>
       </c>
@@ -35991,7 +35450,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="287" spans="1:15">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A287" t="s">
         <v>4036</v>
       </c>
@@ -36038,7 +35497,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="288" spans="1:15">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A288" t="s">
         <v>4051</v>
       </c>
@@ -36085,7 +35544,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="289" spans="1:15">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A289" t="s">
         <v>4065</v>
       </c>
@@ -36132,7 +35591,7 @@
         <v>4079</v>
       </c>
     </row>
-    <row r="290" spans="1:15">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A290" t="s">
         <v>4080</v>
       </c>
@@ -36179,7 +35638,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="291" spans="1:15">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A291" t="s">
         <v>4094</v>
       </c>
@@ -36226,7 +35685,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="292" spans="1:15">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A292" t="s">
         <v>4108</v>
       </c>
@@ -36273,7 +35732,7 @@
         <v>4115</v>
       </c>
     </row>
-    <row r="293" spans="1:15">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A293" t="s">
         <v>4116</v>
       </c>
@@ -36320,7 +35779,7 @@
         <v>4130</v>
       </c>
     </row>
-    <row r="294" spans="1:15">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A294" t="s">
         <v>4131</v>
       </c>
@@ -36367,7 +35826,7 @@
         <v>4145</v>
       </c>
     </row>
-    <row r="295" spans="1:15">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A295" t="s">
         <v>4146</v>
       </c>
@@ -36414,7 +35873,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="296" spans="1:15">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A296" t="s">
         <v>4160</v>
       </c>
@@ -36461,7 +35920,7 @@
         <v>4174</v>
       </c>
     </row>
-    <row r="297" spans="1:15">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A297" t="s">
         <v>4175</v>
       </c>
@@ -36508,7 +35967,7 @@
         <v>4189</v>
       </c>
     </row>
-    <row r="298" spans="1:15">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A298" t="s">
         <v>4190</v>
       </c>
@@ -36555,7 +36014,7 @@
         <v>4204</v>
       </c>
     </row>
-    <row r="299" spans="1:15">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A299" t="s">
         <v>4205</v>
       </c>
@@ -36602,7 +36061,7 @@
         <v>4219</v>
       </c>
     </row>
-    <row r="300" spans="1:15">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A300" t="s">
         <v>4220</v>
       </c>
@@ -36649,7 +36108,7 @@
         <v>4234</v>
       </c>
     </row>
-    <row r="301" spans="1:15">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A301" t="s">
         <v>4235</v>
       </c>
@@ -36696,7 +36155,7 @@
         <v>4249</v>
       </c>
     </row>
-    <row r="302" spans="1:15">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A302" t="s">
         <v>4250</v>
       </c>
@@ -36743,7 +36202,7 @@
         <v>4264</v>
       </c>
     </row>
-    <row r="303" spans="1:15">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A303" t="s">
         <v>4265</v>
       </c>
@@ -36790,7 +36249,7 @@
         <v>4277</v>
       </c>
     </row>
-    <row r="304" spans="1:15">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A304" t="s">
         <v>4278</v>
       </c>
@@ -36837,7 +36296,7 @@
         <v>4279</v>
       </c>
     </row>
-    <row r="305" spans="1:15">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A305" t="s">
         <v>4290</v>
       </c>
@@ -36884,7 +36343,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="306" spans="1:15">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A306" t="s">
         <v>4305</v>
       </c>
@@ -36931,7 +36390,7 @@
         <v>4306</v>
       </c>
     </row>
-    <row r="307" spans="1:15">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A307" t="s">
         <v>4319</v>
       </c>
@@ -36978,7 +36437,7 @@
         <v>4333</v>
       </c>
     </row>
-    <row r="308" spans="1:15">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A308" t="s">
         <v>4334</v>
       </c>
@@ -37025,7 +36484,7 @@
         <v>4348</v>
       </c>
     </row>
-    <row r="309" spans="1:15">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A309" t="s">
         <v>4349</v>
       </c>
@@ -37072,7 +36531,7 @@
         <v>4363</v>
       </c>
     </row>
-    <row r="310" spans="1:15">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A310" t="s">
         <v>4364</v>
       </c>
@@ -37119,7 +36578,7 @@
         <v>4378</v>
       </c>
     </row>
-    <row r="311" spans="1:15">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A311" t="s">
         <v>4379</v>
       </c>
@@ -37166,7 +36625,7 @@
         <v>4393</v>
       </c>
     </row>
-    <row r="312" spans="1:15">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A312" t="s">
         <v>4394</v>
       </c>
@@ -37213,7 +36672,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="313" spans="1:15">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A313" t="s">
         <v>4409</v>
       </c>
@@ -37260,7 +36719,7 @@
         <v>4423</v>
       </c>
     </row>
-    <row r="314" spans="1:15">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A314" t="s">
         <v>4424</v>
       </c>
@@ -37307,7 +36766,7 @@
         <v>4438</v>
       </c>
     </row>
-    <row r="315" spans="1:15">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A315" t="s">
         <v>4439</v>
       </c>
@@ -37354,7 +36813,7 @@
         <v>4453</v>
       </c>
     </row>
-    <row r="316" spans="1:15">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A316" t="s">
         <v>4454</v>
       </c>
@@ -37401,7 +36860,7 @@
         <v>4468</v>
       </c>
     </row>
-    <row r="317" spans="1:15">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A317" t="s">
         <v>4469</v>
       </c>
@@ -37448,7 +36907,7 @@
         <v>4470</v>
       </c>
     </row>
-    <row r="318" spans="1:15">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A318" t="s">
         <v>4483</v>
       </c>
@@ -37495,7 +36954,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="319" spans="1:15">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A319" t="s">
         <v>4497</v>
       </c>
@@ -37542,7 +37001,7 @@
         <v>4511</v>
       </c>
     </row>
-    <row r="320" spans="1:15">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A320" t="s">
         <v>4512</v>
       </c>
@@ -37589,7 +37048,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="321" spans="1:15">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A321" t="s">
         <v>4527</v>
       </c>
@@ -37636,7 +37095,7 @@
         <v>4528</v>
       </c>
     </row>
-    <row r="322" spans="1:15">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A322" t="s">
         <v>4541</v>
       </c>
@@ -37683,7 +37142,7 @@
         <v>4542</v>
       </c>
     </row>
-    <row r="323" spans="1:15">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A323" t="s">
         <v>4555</v>
       </c>
@@ -37730,7 +37189,7 @@
         <v>4556</v>
       </c>
     </row>
-    <row r="324" spans="1:15">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A324" t="s">
         <v>4569</v>
       </c>
@@ -37777,7 +37236,7 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="325" spans="1:15">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A325" t="s">
         <v>4583</v>
       </c>
@@ -37824,7 +37283,7 @@
         <v>4597</v>
       </c>
     </row>
-    <row r="326" spans="1:15">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A326" t="s">
         <v>4598</v>
       </c>
@@ -37871,7 +37330,7 @@
         <v>4612</v>
       </c>
     </row>
-    <row r="327" spans="1:15">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A327" t="s">
         <v>4613</v>
       </c>
@@ -37918,7 +37377,7 @@
         <v>4627</v>
       </c>
     </row>
-    <row r="328" spans="1:15">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A328" t="s">
         <v>4628</v>
       </c>
@@ -37965,7 +37424,7 @@
         <v>4642</v>
       </c>
     </row>
-    <row r="329" spans="1:15">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A329" t="s">
         <v>4643</v>
       </c>
@@ -38012,7 +37471,7 @@
         <v>4657</v>
       </c>
     </row>
-    <row r="330" spans="1:15">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A330" t="s">
         <v>4658</v>
       </c>
@@ -38059,7 +37518,7 @@
         <v>4672</v>
       </c>
     </row>
-    <row r="331" spans="1:15">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A331" t="s">
         <v>4673</v>
       </c>
@@ -38106,7 +37565,7 @@
         <v>4674</v>
       </c>
     </row>
-    <row r="332" spans="1:15">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A332" t="s">
         <v>4687</v>
       </c>
@@ -38153,7 +37612,7 @@
         <v>4688</v>
       </c>
     </row>
-    <row r="333" spans="1:15">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A333" t="s">
         <v>4701</v>
       </c>
@@ -38200,7 +37659,7 @@
         <v>4715</v>
       </c>
     </row>
-    <row r="334" spans="1:15">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A334" t="s">
         <v>4716</v>
       </c>
@@ -38247,7 +37706,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="335" spans="1:15">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A335" t="s">
         <v>4731</v>
       </c>
@@ -38294,7 +37753,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="336" spans="1:15">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A336" t="s">
         <v>4745</v>
       </c>
@@ -38341,7 +37800,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="337" spans="1:15">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A337" t="s">
         <v>4758</v>
       </c>
@@ -38388,7 +37847,7 @@
         <v>4772</v>
       </c>
     </row>
-    <row r="338" spans="1:15">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A338" t="s">
         <v>4773</v>
       </c>
@@ -38435,7 +37894,7 @@
         <v>4786</v>
       </c>
     </row>
-    <row r="339" spans="1:15">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A339" t="s">
         <v>4787</v>
       </c>
@@ -38482,7 +37941,7 @@
         <v>4790</v>
       </c>
     </row>
-    <row r="340" spans="1:15">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A340" t="s">
         <v>4799</v>
       </c>
@@ -38529,7 +37988,7 @@
         <v>4813</v>
       </c>
     </row>
-    <row r="341" spans="1:15">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A341" t="s">
         <v>4814</v>
       </c>
@@ -38576,7 +38035,7 @@
         <v>4828</v>
       </c>
     </row>
-    <row r="342" spans="1:15">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A342" t="s">
         <v>4829</v>
       </c>
@@ -38623,7 +38082,7 @@
         <v>4830</v>
       </c>
     </row>
-    <row r="343" spans="1:15">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A343" t="s">
         <v>4839</v>
       </c>
@@ -38670,7 +38129,7 @@
         <v>4840</v>
       </c>
     </row>
-    <row r="344" spans="1:15">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A344" t="s">
         <v>4853</v>
       </c>
@@ -38717,7 +38176,7 @@
         <v>4866</v>
       </c>
     </row>
-    <row r="345" spans="1:15">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A345" t="s">
         <v>4867</v>
       </c>
@@ -38764,7 +38223,7 @@
         <v>4868</v>
       </c>
     </row>
-    <row r="346" spans="1:15">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A346" t="s">
         <v>4881</v>
       </c>
@@ -38811,7 +38270,7 @@
         <v>4894</v>
       </c>
     </row>
-    <row r="347" spans="1:15">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A347" t="s">
         <v>4895</v>
       </c>
@@ -38858,7 +38317,7 @@
         <v>4896</v>
       </c>
     </row>
-    <row r="348" spans="1:15">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A348" t="s">
         <v>4905</v>
       </c>
@@ -38905,7 +38364,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="349" spans="1:15">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A349" t="s">
         <v>4920</v>
       </c>
@@ -38952,7 +38411,7 @@
         <v>4934</v>
       </c>
     </row>
-    <row r="350" spans="1:15">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A350" t="s">
         <v>4935</v>
       </c>
@@ -38999,7 +38458,7 @@
         <v>4949</v>
       </c>
     </row>
-    <row r="351" spans="1:15">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A351" t="s">
         <v>4950</v>
       </c>
@@ -39046,7 +38505,7 @@
         <v>4951</v>
       </c>
     </row>
-    <row r="352" spans="1:15">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A352" t="s">
         <v>4964</v>
       </c>
@@ -39093,7 +38552,7 @@
         <v>4977</v>
       </c>
     </row>
-    <row r="353" spans="1:15">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A353" t="s">
         <v>4978</v>
       </c>
@@ -39140,7 +38599,7 @@
         <v>4992</v>
       </c>
     </row>
-    <row r="354" spans="1:15">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A354" t="s">
         <v>4993</v>
       </c>
@@ -39187,7 +38646,7 @@
         <v>5007</v>
       </c>
     </row>
-    <row r="355" spans="1:15">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A355" t="s">
         <v>5008</v>
       </c>
@@ -39234,7 +38693,7 @@
         <v>5022</v>
       </c>
     </row>
-    <row r="356" spans="1:15">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A356" t="s">
         <v>5023</v>
       </c>
@@ -39281,7 +38740,7 @@
         <v>5037</v>
       </c>
     </row>
-    <row r="357" spans="1:15">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A357" t="s">
         <v>5038</v>
       </c>
@@ -39328,7 +38787,7 @@
         <v>5039</v>
       </c>
     </row>
-    <row r="358" spans="1:15">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A358" t="s">
         <v>5052</v>
       </c>
@@ -39375,7 +38834,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="359" spans="1:15">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A359" t="s">
         <v>5064</v>
       </c>
@@ -39422,7 +38881,7 @@
         <v>5076</v>
       </c>
     </row>
-    <row r="360" spans="1:15">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A360" t="s">
         <v>5077</v>
       </c>
@@ -39469,7 +38928,7 @@
         <v>5091</v>
       </c>
     </row>
-    <row r="361" spans="1:15">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A361" t="s">
         <v>5092</v>
       </c>
@@ -39516,7 +38975,7 @@
         <v>5093</v>
       </c>
     </row>
-    <row r="362" spans="1:15">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A362" t="s">
         <v>5106</v>
       </c>
@@ -39563,7 +39022,7 @@
         <v>5120</v>
       </c>
     </row>
-    <row r="363" spans="1:15">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A363" t="s">
         <v>5121</v>
       </c>
@@ -39610,7 +39069,7 @@
         <v>5135</v>
       </c>
     </row>
-    <row r="364" spans="1:15">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A364" t="s">
         <v>5136</v>
       </c>
@@ -39657,7 +39116,7 @@
         <v>5137</v>
       </c>
     </row>
-    <row r="365" spans="1:15">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A365" t="s">
         <v>5150</v>
       </c>
@@ -39704,7 +39163,7 @@
         <v>5164</v>
       </c>
     </row>
-    <row r="366" spans="1:15">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A366" t="s">
         <v>5165</v>
       </c>
@@ -39751,7 +39210,7 @@
         <v>5166</v>
       </c>
     </row>
-    <row r="367" spans="1:15">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A367" t="s">
         <v>5179</v>
       </c>
@@ -39798,7 +39257,7 @@
         <v>5193</v>
       </c>
     </row>
-    <row r="368" spans="1:15">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A368" t="s">
         <v>5194</v>
       </c>
@@ -39845,7 +39304,7 @@
         <v>5195</v>
       </c>
     </row>
-    <row r="369" spans="1:15">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A369" t="s">
         <v>5208</v>
       </c>
@@ -39892,7 +39351,7 @@
         <v>5209</v>
       </c>
     </row>
-    <row r="370" spans="1:15">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A370" t="s">
         <v>5222</v>
       </c>
@@ -39939,7 +39398,7 @@
         <v>5223</v>
       </c>
     </row>
-    <row r="371" spans="1:15">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A371" t="s">
         <v>5236</v>
       </c>
@@ -39986,7 +39445,7 @@
         <v>5237</v>
       </c>
     </row>
-    <row r="372" spans="1:15">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A372" t="s">
         <v>5248</v>
       </c>
@@ -40033,7 +39492,7 @@
         <v>5261</v>
       </c>
     </row>
-    <row r="373" spans="1:15">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A373" t="s">
         <v>5262</v>
       </c>
@@ -40080,7 +39539,7 @@
         <v>5276</v>
       </c>
     </row>
-    <row r="374" spans="1:15">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A374" t="s">
         <v>5277</v>
       </c>
@@ -40127,7 +39586,7 @@
         <v>5278</v>
       </c>
     </row>
-    <row r="375" spans="1:15">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A375" t="s">
         <v>5291</v>
       </c>
@@ -40174,7 +39633,7 @@
         <v>5305</v>
       </c>
     </row>
-    <row r="376" spans="1:15">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A376" t="s">
         <v>5306</v>
       </c>
@@ -40221,7 +39680,7 @@
         <v>5320</v>
       </c>
     </row>
-    <row r="377" spans="1:15">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A377" t="s">
         <v>5321</v>
       </c>
@@ -40268,7 +39727,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="378" spans="1:15">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A378" t="s">
         <v>5336</v>
       </c>
@@ -40315,7 +39774,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="379" spans="1:15">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A379" t="s">
         <v>5338</v>
       </c>
@@ -40362,7 +39821,7 @@
         <v>5352</v>
       </c>
     </row>
-    <row r="380" spans="1:15">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A380" t="s">
         <v>5353</v>
       </c>
@@ -40409,7 +39868,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="381" spans="1:15">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A381" t="s">
         <v>5365</v>
       </c>
@@ -40456,7 +39915,7 @@
         <v>5379</v>
       </c>
     </row>
-    <row r="382" spans="1:15">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A382" t="s">
         <v>5380</v>
       </c>
@@ -40503,7 +39962,7 @@
         <v>5390</v>
       </c>
     </row>
-    <row r="383" spans="1:15">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A383" t="s">
         <v>5391</v>
       </c>
@@ -40550,7 +40009,7 @@
         <v>5405</v>
       </c>
     </row>
-    <row r="384" spans="1:15">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A384" t="s">
         <v>5406</v>
       </c>
@@ -40597,7 +40056,7 @@
         <v>5407</v>
       </c>
     </row>
-    <row r="385" spans="1:15">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A385" t="s">
         <v>5418</v>
       </c>
@@ -40644,7 +40103,7 @@
         <v>5432</v>
       </c>
     </row>
-    <row r="386" spans="1:15">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A386" t="s">
         <v>5433</v>
       </c>
@@ -40691,7 +40150,7 @@
         <v>5447</v>
       </c>
     </row>
-    <row r="387" spans="1:15">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A387" t="s">
         <v>5448</v>
       </c>
@@ -40738,7 +40197,7 @@
         <v>5449</v>
       </c>
     </row>
-    <row r="388" spans="1:15">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A388" t="s">
         <v>5461</v>
       </c>
@@ -40785,7 +40244,7 @@
         <v>5474</v>
       </c>
     </row>
-    <row r="389" spans="1:15">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A389" t="s">
         <v>5475</v>
       </c>
@@ -40832,7 +40291,7 @@
         <v>5489</v>
       </c>
     </row>
-    <row r="390" spans="1:15">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A390" t="s">
         <v>5490</v>
       </c>
@@ -40879,7 +40338,7 @@
         <v>5504</v>
       </c>
     </row>
-    <row r="391" spans="1:15">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A391" t="s">
         <v>5505</v>
       </c>
@@ -40926,7 +40385,7 @@
         <v>5506</v>
       </c>
     </row>
-    <row r="392" spans="1:15">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A392" t="s">
         <v>5519</v>
       </c>
@@ -40973,7 +40432,7 @@
         <v>5520</v>
       </c>
     </row>
-    <row r="393" spans="1:15">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A393" t="s">
         <v>5529</v>
       </c>
@@ -41020,7 +40479,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="394" spans="1:15">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A394" t="s">
         <v>5544</v>
       </c>
@@ -41067,7 +40526,7 @@
         <v>5558</v>
       </c>
     </row>
-    <row r="395" spans="1:15">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A395" t="s">
         <v>5559</v>
       </c>
@@ -41114,7 +40573,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="396" spans="1:15">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A396" t="s">
         <v>5573</v>
       </c>
@@ -41161,7 +40620,7 @@
         <v>5587</v>
       </c>
     </row>
-    <row r="397" spans="1:15">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A397" t="s">
         <v>5588</v>
       </c>
@@ -41208,7 +40667,7 @@
         <v>5602</v>
       </c>
     </row>
-    <row r="398" spans="1:15">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A398" t="s">
         <v>5603</v>
       </c>
@@ -41255,7 +40714,7 @@
         <v>5617</v>
       </c>
     </row>
-    <row r="399" spans="1:15">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A399" t="s">
         <v>5618</v>
       </c>
@@ -41302,7 +40761,7 @@
         <v>5632</v>
       </c>
     </row>
-    <row r="400" spans="1:15">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A400" t="s">
         <v>5633</v>
       </c>
@@ -41349,7 +40808,7 @@
         <v>5634</v>
       </c>
     </row>
-    <row r="401" spans="1:15">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A401" t="s">
         <v>5647</v>
       </c>
@@ -41396,7 +40855,7 @@
         <v>5661</v>
       </c>
     </row>
-    <row r="402" spans="1:15">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A402" t="s">
         <v>5662</v>
       </c>
@@ -41443,7 +40902,7 @@
         <v>5663</v>
       </c>
     </row>
-    <row r="403" spans="1:15">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A403" t="s">
         <v>5674</v>
       </c>
@@ -41490,7 +40949,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="404" spans="1:15">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A404" t="s">
         <v>5687</v>
       </c>
@@ -41537,7 +40996,7 @@
         <v>5699</v>
       </c>
     </row>
-    <row r="405" spans="1:15">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A405" t="s">
         <v>5700</v>
       </c>
@@ -41584,7 +41043,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="406" spans="1:15">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A406" t="s">
         <v>5715</v>
       </c>
@@ -41631,7 +41090,7 @@
         <v>5729</v>
       </c>
     </row>
-    <row r="407" spans="1:15">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A407" t="s">
         <v>5730</v>
       </c>
@@ -41678,7 +41137,7 @@
         <v>5744</v>
       </c>
     </row>
-    <row r="408" spans="1:15">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A408" t="s">
         <v>5745</v>
       </c>
@@ -41725,7 +41184,7 @@
         <v>5746</v>
       </c>
     </row>
-    <row r="409" spans="1:15">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A409" t="s">
         <v>5759</v>
       </c>
@@ -41772,7 +41231,7 @@
         <v>5760</v>
       </c>
     </row>
-    <row r="410" spans="1:15">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A410" t="s">
         <v>5772</v>
       </c>
@@ -41819,7 +41278,7 @@
         <v>5786</v>
       </c>
     </row>
-    <row r="411" spans="1:15">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A411" t="s">
         <v>5787</v>
       </c>
@@ -41866,7 +41325,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="412" spans="1:15">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A412" t="s">
         <v>5802</v>
       </c>
@@ -41913,7 +41372,7 @@
         <v>5816</v>
       </c>
     </row>
-    <row r="413" spans="1:15">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A413" t="s">
         <v>5817</v>
       </c>
@@ -41960,7 +41419,7 @@
         <v>5831</v>
       </c>
     </row>
-    <row r="414" spans="1:15">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A414" t="s">
         <v>5832</v>
       </c>
@@ -42007,7 +41466,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="415" spans="1:15">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A415" t="s">
         <v>5846</v>
       </c>
@@ -42054,7 +41513,7 @@
         <v>5860</v>
       </c>
     </row>
-    <row r="416" spans="1:15">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A416" t="s">
         <v>5861</v>
       </c>
@@ -42101,7 +41560,7 @@
         <v>5874</v>
       </c>
     </row>
-    <row r="417" spans="1:15">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A417" t="s">
         <v>5875</v>
       </c>
@@ -42148,7 +41607,7 @@
         <v>5889</v>
       </c>
     </row>
-    <row r="418" spans="1:15">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A418" t="s">
         <v>5890</v>
       </c>
@@ -42195,7 +41654,7 @@
         <v>5891</v>
       </c>
     </row>
-    <row r="419" spans="1:15">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A419" t="s">
         <v>5904</v>
       </c>
@@ -42242,7 +41701,7 @@
         <v>5905</v>
       </c>
     </row>
-    <row r="420" spans="1:15">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A420" t="s">
         <v>5918</v>
       </c>
@@ -42289,7 +41748,7 @@
         <v>5932</v>
       </c>
     </row>
-    <row r="421" spans="1:15">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A421" t="s">
         <v>5933</v>
       </c>
@@ -42336,7 +41795,7 @@
         <v>5947</v>
       </c>
     </row>
-    <row r="422" spans="1:15">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A422" t="s">
         <v>5948</v>
       </c>
@@ -42383,7 +41842,7 @@
         <v>5962</v>
       </c>
     </row>
-    <row r="423" spans="1:15">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A423" t="s">
         <v>5963</v>
       </c>
@@ -42430,7 +41889,7 @@
         <v>5977</v>
       </c>
     </row>
-    <row r="424" spans="1:15">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A424" t="s">
         <v>5978</v>
       </c>
@@ -42477,7 +41936,7 @@
         <v>5992</v>
       </c>
     </row>
-    <row r="425" spans="1:15">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A425" t="s">
         <v>5993</v>
       </c>
@@ -42524,7 +41983,7 @@
         <v>6007</v>
       </c>
     </row>
-    <row r="426" spans="1:15">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A426" t="s">
         <v>6008</v>
       </c>
@@ -42571,7 +42030,7 @@
         <v>6009</v>
       </c>
     </row>
-    <row r="427" spans="1:15">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A427" t="s">
         <v>6022</v>
       </c>
@@ -42618,7 +42077,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="428" spans="1:15">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A428" t="s">
         <v>6031</v>
       </c>
@@ -42665,7 +42124,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="429" spans="1:15">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A429" t="s">
         <v>6038</v>
       </c>
@@ -42712,7 +42171,7 @@
         <v>6039</v>
       </c>
     </row>
-    <row r="430" spans="1:15">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A430" t="s">
         <v>6052</v>
       </c>
@@ -42759,7 +42218,7 @@
         <v>6066</v>
       </c>
     </row>
-    <row r="431" spans="1:15">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A431" t="s">
         <v>6067</v>
       </c>
@@ -42806,7 +42265,7 @@
         <v>6068</v>
       </c>
     </row>
-    <row r="432" spans="1:15">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A432" t="s">
         <v>6080</v>
       </c>
@@ -42853,7 +42312,7 @@
         <v>6094</v>
       </c>
     </row>
-    <row r="433" spans="1:15">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A433" t="s">
         <v>6095</v>
       </c>
@@ -42900,7 +42359,7 @@
         <v>6109</v>
       </c>
     </row>
-    <row r="434" spans="1:15">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A434" t="s">
         <v>6110</v>
       </c>
@@ -42947,7 +42406,7 @@
         <v>6124</v>
       </c>
     </row>
-    <row r="435" spans="1:15">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A435" t="s">
         <v>6125</v>
       </c>
@@ -42994,7 +42453,7 @@
         <v>6139</v>
       </c>
     </row>
-    <row r="436" spans="1:15">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A436" t="s">
         <v>6140</v>
       </c>
@@ -43041,7 +42500,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="437" spans="1:15">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A437" t="s">
         <v>6153</v>
       </c>
@@ -43088,7 +42547,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="438" spans="1:15">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A438" t="s">
         <v>6159</v>
       </c>
@@ -43135,7 +42594,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="439" spans="1:15">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A439" t="s">
         <v>6167</v>
       </c>
@@ -43182,7 +42641,7 @@
         <v>4145</v>
       </c>
     </row>
-    <row r="440" spans="1:15">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A440" t="s">
         <v>6179</v>
       </c>
@@ -43229,7 +42688,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="441" spans="1:15">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A441" t="s">
         <v>6193</v>
       </c>
@@ -43276,7 +42735,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="442" spans="1:15">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A442" t="s">
         <v>6206</v>
       </c>
@@ -43323,7 +42782,7 @@
         <v>4174</v>
       </c>
     </row>
-    <row r="443" spans="1:15">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A443" t="s">
         <v>6211</v>
       </c>
@@ -43370,7 +42829,7 @@
         <v>6225</v>
       </c>
     </row>
-    <row r="444" spans="1:15">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A444" t="s">
         <v>6226</v>
       </c>
@@ -43417,7 +42876,7 @@
         <v>6240</v>
       </c>
     </row>
-    <row r="445" spans="1:15">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A445" t="s">
         <v>6241</v>
       </c>
@@ -43464,7 +42923,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="446" spans="1:15">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A446" t="s">
         <v>6256</v>
       </c>
@@ -43511,7 +42970,7 @@
         <v>6270</v>
       </c>
     </row>
-    <row r="447" spans="1:15">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A447" t="s">
         <v>6271</v>
       </c>
@@ -43558,7 +43017,7 @@
         <v>6284</v>
       </c>
     </row>
-    <row r="448" spans="1:15">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A448" t="s">
         <v>6285</v>
       </c>
@@ -43605,7 +43064,7 @@
         <v>6298</v>
       </c>
     </row>
-    <row r="449" spans="1:15">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A449" t="s">
         <v>6299</v>
       </c>
@@ -43652,7 +43111,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="450" spans="1:15">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A450" t="s">
         <v>6305</v>
       </c>
@@ -43699,7 +43158,7 @@
         <v>6312</v>
       </c>
     </row>
-    <row r="451" spans="1:15">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A451" t="s">
         <v>6313</v>
       </c>
@@ -43746,7 +43205,7 @@
         <v>6327</v>
       </c>
     </row>
-    <row r="452" spans="1:15">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A452" t="s">
         <v>6328</v>
       </c>
@@ -43793,7 +43252,7 @@
         <v>6342</v>
       </c>
     </row>
-    <row r="453" spans="1:15">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A453" t="s">
         <v>6343</v>
       </c>
@@ -43840,7 +43299,7 @@
         <v>6344</v>
       </c>
     </row>
-    <row r="454" spans="1:15">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A454" t="s">
         <v>6357</v>
       </c>
@@ -43887,7 +43346,7 @@
         <v>6360</v>
       </c>
     </row>
-    <row r="455" spans="1:15">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A455" t="s">
         <v>6370</v>
       </c>
@@ -43934,7 +43393,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="456" spans="1:15">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A456" t="s">
         <v>6382</v>
       </c>
@@ -43981,7 +43440,7 @@
         <v>6385</v>
       </c>
     </row>
-    <row r="457" spans="1:15">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A457" t="s">
         <v>6396</v>
       </c>
@@ -44028,7 +43487,7 @@
         <v>6410</v>
       </c>
     </row>
-    <row r="458" spans="1:15">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A458" t="s">
         <v>6411</v>
       </c>
@@ -44075,7 +43534,7 @@
         <v>6425</v>
       </c>
     </row>
-    <row r="459" spans="1:15">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A459" t="s">
         <v>6426</v>
       </c>
@@ -44122,7 +43581,7 @@
         <v>6440</v>
       </c>
     </row>
-    <row r="460" spans="1:15">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A460" t="s">
         <v>6441</v>
       </c>
@@ -44169,7 +43628,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="461" spans="1:15">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A461" t="s">
         <v>6456</v>
       </c>
@@ -44216,7 +43675,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="462" spans="1:15">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A462" t="s">
         <v>6471</v>
       </c>
@@ -44263,7 +43722,7 @@
         <v>6485</v>
       </c>
     </row>
-    <row r="463" spans="1:15">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A463" t="s">
         <v>6486</v>
       </c>
@@ -44310,7 +43769,7 @@
         <v>6499</v>
       </c>
     </row>
-    <row r="464" spans="1:15">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A464" t="s">
         <v>6500</v>
       </c>
@@ -44357,7 +43816,7 @@
         <v>6513</v>
       </c>
     </row>
-    <row r="465" spans="1:15">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A465" t="s">
         <v>6514</v>
       </c>
@@ -44404,7 +43863,7 @@
         <v>6528</v>
       </c>
     </row>
-    <row r="466" spans="1:15">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A466" t="s">
         <v>6529</v>
       </c>
@@ -44451,7 +43910,7 @@
         <v>6543</v>
       </c>
     </row>
-    <row r="467" spans="1:15">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A467" t="s">
         <v>6544</v>
       </c>
@@ -44498,7 +43957,7 @@
         <v>6557</v>
       </c>
     </row>
-    <row r="468" spans="1:15">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A468" t="s">
         <v>6558</v>
       </c>
@@ -44545,7 +44004,7 @@
         <v>6572</v>
       </c>
     </row>
-    <row r="469" spans="1:15">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A469" t="s">
         <v>6573</v>
       </c>
@@ -44592,7 +44051,7 @@
         <v>6574</v>
       </c>
     </row>
-    <row r="470" spans="1:15">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A470" t="s">
         <v>6586</v>
       </c>
@@ -44639,7 +44098,7 @@
         <v>6587</v>
       </c>
     </row>
-    <row r="471" spans="1:15">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A471" t="s">
         <v>6600</v>
       </c>
@@ -44686,7 +44145,7 @@
         <v>6601</v>
       </c>
     </row>
-    <row r="472" spans="1:15">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A472" t="s">
         <v>6613</v>
       </c>
@@ -44733,7 +44192,7 @@
         <v>6618</v>
       </c>
     </row>
-    <row r="473" spans="1:15">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A473" t="s">
         <v>6619</v>
       </c>
@@ -44780,7 +44239,7 @@
         <v>6633</v>
       </c>
     </row>
-    <row r="474" spans="1:15">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A474" t="s">
         <v>6634</v>
       </c>
@@ -44827,7 +44286,7 @@
         <v>6648</v>
       </c>
     </row>
-    <row r="475" spans="1:15">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A475" t="s">
         <v>6649</v>
       </c>
@@ -44874,7 +44333,7 @@
         <v>6658</v>
       </c>
     </row>
-    <row r="476" spans="1:15">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A476" t="s">
         <v>6659</v>
       </c>
@@ -44921,7 +44380,7 @@
         <v>6672</v>
       </c>
     </row>
-    <row r="477" spans="1:15">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A477" t="s">
         <v>6673</v>
       </c>
@@ -44968,7 +44427,7 @@
         <v>6687</v>
       </c>
     </row>
-    <row r="478" spans="1:15">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A478" t="s">
         <v>6688</v>
       </c>
@@ -45015,7 +44474,7 @@
         <v>6702</v>
       </c>
     </row>
-    <row r="479" spans="1:15">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A479" t="s">
         <v>6703</v>
       </c>
@@ -45062,7 +44521,7 @@
         <v>6717</v>
       </c>
     </row>
-    <row r="480" spans="1:15">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A480" t="s">
         <v>6718</v>
       </c>
@@ -45109,7 +44568,7 @@
         <v>6732</v>
       </c>
     </row>
-    <row r="481" spans="1:15">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A481" t="s">
         <v>6733</v>
       </c>
@@ -45156,7 +44615,7 @@
         <v>6747</v>
       </c>
     </row>
-    <row r="482" spans="1:15">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A482" t="s">
         <v>6748</v>
       </c>
@@ -45203,7 +44662,7 @@
         <v>6762</v>
       </c>
     </row>
-    <row r="483" spans="1:15">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A483" t="s">
         <v>6763</v>
       </c>
@@ -45250,7 +44709,7 @@
         <v>6777</v>
       </c>
     </row>
-    <row r="484" spans="1:15">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A484" t="s">
         <v>6778</v>
       </c>
@@ -45297,7 +44756,7 @@
         <v>6792</v>
       </c>
     </row>
-    <row r="485" spans="1:15">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A485" t="s">
         <v>6793</v>
       </c>
@@ -45344,7 +44803,7 @@
         <v>6807</v>
       </c>
     </row>
-    <row r="486" spans="1:15">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A486" t="s">
         <v>6808</v>
       </c>
@@ -45391,7 +44850,7 @@
         <v>6822</v>
       </c>
     </row>
-    <row r="487" spans="1:15">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A487" t="s">
         <v>6823</v>
       </c>
@@ -45438,7 +44897,7 @@
         <v>6837</v>
       </c>
     </row>
-    <row r="488" spans="1:15">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A488" t="s">
         <v>6838</v>
       </c>
@@ -45485,7 +44944,7 @@
         <v>6852</v>
       </c>
     </row>
-    <row r="489" spans="1:15">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A489" t="s">
         <v>6853</v>
       </c>
@@ -45532,7 +44991,7 @@
         <v>6867</v>
       </c>
     </row>
-    <row r="490" spans="1:15">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A490" t="s">
         <v>6868</v>
       </c>
@@ -45579,7 +45038,7 @@
         <v>6882</v>
       </c>
     </row>
-    <row r="491" spans="1:15">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A491" t="s">
         <v>6883</v>
       </c>
@@ -45626,7 +45085,7 @@
         <v>6897</v>
       </c>
     </row>
-    <row r="492" spans="1:15">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A492" t="s">
         <v>6898</v>
       </c>
@@ -45673,7 +45132,7 @@
         <v>6912</v>
       </c>
     </row>
-    <row r="493" spans="1:15">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A493" t="s">
         <v>6913</v>
       </c>
@@ -45720,7 +45179,7 @@
         <v>6927</v>
       </c>
     </row>
-    <row r="494" spans="1:15">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A494" t="s">
         <v>6928</v>
       </c>
@@ -45767,7 +45226,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="495" spans="1:15">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A495" t="s">
         <v>6943</v>
       </c>
@@ -45814,7 +45273,7 @@
         <v>6957</v>
       </c>
     </row>
-    <row r="496" spans="1:15">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A496" t="s">
         <v>6958</v>
       </c>
@@ -45861,7 +45320,7 @@
         <v>6972</v>
       </c>
     </row>
-    <row r="497" spans="1:15">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A497" t="s">
         <v>6973</v>
       </c>
@@ -45908,7 +45367,7 @@
         <v>6987</v>
       </c>
     </row>
-    <row r="498" spans="1:15">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A498" t="s">
         <v>6988</v>
       </c>
@@ -45955,7 +45414,7 @@
         <v>7002</v>
       </c>
     </row>
-    <row r="499" spans="1:15">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A499" t="s">
         <v>7003</v>
       </c>
@@ -46002,7 +45461,7 @@
         <v>7004</v>
       </c>
     </row>
-    <row r="500" spans="1:15">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A500" t="s">
         <v>7017</v>
       </c>
@@ -46049,7 +45508,7 @@
         <v>7019</v>
       </c>
     </row>
-    <row r="501" spans="1:15">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A501" t="s">
         <v>7020</v>
       </c>
@@ -46096,7 +45555,7 @@
         <v>7034</v>
       </c>
     </row>
-    <row r="502" spans="1:15">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A502" t="s">
         <v>7035</v>
       </c>
@@ -46143,7 +45602,7 @@
         <v>7049</v>
       </c>
     </row>
-    <row r="503" spans="1:15">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A503" t="s">
         <v>7050</v>
       </c>
@@ -46190,7 +45649,7 @@
         <v>7052</v>
       </c>
     </row>
-    <row r="504" spans="1:15">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A504" t="s">
         <v>7053</v>
       </c>
@@ -46237,7 +45696,7 @@
         <v>7054</v>
       </c>
     </row>
-    <row r="505" spans="1:15">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A505" t="s">
         <v>7067</v>
       </c>
@@ -46284,7 +45743,7 @@
         <v>7081</v>
       </c>
     </row>
-    <row r="506" spans="1:15">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A506" t="s">
         <v>7082</v>
       </c>
@@ -46331,7 +45790,7 @@
         <v>7096</v>
       </c>
     </row>
-    <row r="507" spans="1:15">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A507" t="s">
         <v>7097</v>
       </c>
@@ -46378,7 +45837,7 @@
         <v>7111</v>
       </c>
     </row>
-    <row r="508" spans="1:15">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A508" t="s">
         <v>7112</v>
       </c>
@@ -46425,7 +45884,7 @@
         <v>7126</v>
       </c>
     </row>
-    <row r="509" spans="1:15">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A509" t="s">
         <v>7127</v>
       </c>
@@ -46472,7 +45931,7 @@
         <v>7141</v>
       </c>
     </row>
-    <row r="510" spans="1:15">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A510" t="s">
         <v>7142</v>
       </c>
@@ -46519,7 +45978,7 @@
         <v>7143</v>
       </c>
     </row>
-    <row r="511" spans="1:15">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A511" t="s">
         <v>7156</v>
       </c>
@@ -46566,101 +46025,101 @@
         <v>7157</v>
       </c>
     </row>
-    <row r="512" spans="1:15">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A512" t="s">
         <v>7159</v>
       </c>
-      <c r="B512" s="1" t="s">
+      <c r="B512" t="s">
         <v>7160</v>
       </c>
-      <c r="C512" s="1" t="s">
+      <c r="C512" t="s">
         <v>7160</v>
       </c>
-      <c r="D512" s="1" t="s">
+      <c r="D512" t="s">
         <v>7160</v>
       </c>
-      <c r="E512" s="1" t="s">
+      <c r="E512" t="s">
         <v>7160</v>
       </c>
-      <c r="F512" s="1" t="s">
+      <c r="F512" t="s">
         <v>7160</v>
       </c>
-      <c r="G512" s="1" t="s">
+      <c r="G512" t="s">
         <v>7160</v>
       </c>
-      <c r="H512" s="1" t="s">
+      <c r="H512" t="s">
         <v>7160</v>
       </c>
-      <c r="I512" s="1" t="s">
+      <c r="I512" t="s">
         <v>7160</v>
       </c>
-      <c r="J512" s="1" t="s">
+      <c r="J512" t="s">
         <v>7160</v>
       </c>
-      <c r="K512" s="1" t="s">
+      <c r="K512" t="s">
         <v>7160</v>
       </c>
-      <c r="L512" s="1" t="s">
+      <c r="L512" t="s">
         <v>7160</v>
       </c>
-      <c r="M512" s="1" t="s">
+      <c r="M512" t="s">
         <v>7160</v>
       </c>
-      <c r="N512" s="1" t="s">
+      <c r="N512" t="s">
         <v>7160</v>
       </c>
-      <c r="O512" s="1" t="s">
+      <c r="O512" t="s">
         <v>7160</v>
       </c>
     </row>
-    <row r="513" spans="1:15">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A513" t="s">
         <v>7161</v>
       </c>
-      <c r="B513" s="1" t="s">
+      <c r="B513" t="s">
         <v>7162</v>
       </c>
-      <c r="C513" s="1" t="s">
+      <c r="C513" t="s">
         <v>7162</v>
       </c>
-      <c r="D513" s="1" t="s">
+      <c r="D513" t="s">
         <v>7162</v>
       </c>
-      <c r="E513" s="1" t="s">
+      <c r="E513" t="s">
         <v>7162</v>
       </c>
-      <c r="F513" s="1" t="s">
+      <c r="F513" t="s">
         <v>7162</v>
       </c>
-      <c r="G513" s="1" t="s">
+      <c r="G513" t="s">
         <v>7162</v>
       </c>
-      <c r="H513" s="1" t="s">
+      <c r="H513" t="s">
         <v>7162</v>
       </c>
-      <c r="I513" s="1" t="s">
+      <c r="I513" t="s">
         <v>7162</v>
       </c>
-      <c r="J513" s="1" t="s">
+      <c r="J513" t="s">
         <v>7162</v>
       </c>
-      <c r="K513" s="1" t="s">
+      <c r="K513" t="s">
         <v>7162</v>
       </c>
-      <c r="L513" s="1" t="s">
+      <c r="L513" t="s">
         <v>7162</v>
       </c>
-      <c r="M513" s="1" t="s">
+      <c r="M513" t="s">
         <v>7162</v>
       </c>
-      <c r="N513" s="1" t="s">
+      <c r="N513" t="s">
         <v>7162</v>
       </c>
-      <c r="O513" s="1" t="s">
+      <c r="O513" t="s">
         <v>7162</v>
       </c>
     </row>
-    <row r="514" spans="1:15">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A514" t="s">
         <v>7163</v>
       </c>
@@ -46707,9 +46166,386 @@
         <v>7164</v>
       </c>
     </row>
+    <row r="515" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A515" s="1" t="s">
+        <v>7165</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="E515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="F515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="G515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="H515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="I515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="J515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="K515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="L515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="M515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="N515" s="1" t="s">
+        <v>7166</v>
+      </c>
+      <c r="O515" s="1" t="s">
+        <v>7166</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A516" s="1" t="s">
+        <v>7173</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="E516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="F516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="G516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="H516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="I516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="J516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="K516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="L516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="M516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="N516" s="1" t="s">
+        <v>7180</v>
+      </c>
+      <c r="O516" s="1" t="s">
+        <v>7180</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A517" s="2" t="s">
+        <v>7167</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="F517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="G517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="H517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="I517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="J517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="K517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="L517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="M517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="N517" s="1" t="s">
+        <v>7170</v>
+      </c>
+      <c r="O517" s="1" t="s">
+        <v>7170</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A518" s="1" t="s">
+        <v>7168</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="E518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="F518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="G518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="H518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="I518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="J518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="K518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="L518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="M518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="N518" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="O518" s="1" t="s">
+        <v>7171</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A519" s="1" t="s">
+        <v>7169</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="E519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="F519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="G519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="H519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="I519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="J519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="K519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="L519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="M519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="N519" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="O519" s="1" t="s">
+        <v>7172</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A520" s="1" t="s">
+        <v>7174</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="E520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="F520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="G520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="H520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="I520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="J520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="K520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="L520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="M520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="N520" s="1" t="s">
+        <v>7177</v>
+      </c>
+      <c r="O520" s="1" t="s">
+        <v>7177</v>
+      </c>
+    </row>
+    <row r="521" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A521" s="1" t="s">
+        <v>7175</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="D521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="E521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="F521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="G521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="H521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="I521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="J521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="K521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="L521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="M521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="N521" s="1" t="s">
+        <v>7178</v>
+      </c>
+      <c r="O521" s="1" t="s">
+        <v>7178</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A522" s="1" t="s">
+        <v>7176</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="E522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="F522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="G522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="H522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="I522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="J522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="K522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="L522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="M522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="N522" s="1" t="s">
+        <v>7179</v>
+      </c>
+      <c r="O522" s="1" t="s">
+        <v>7179</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A279:O449 A450 C450:O450 A451:O499 C118:O118 A504:O510 A503 A501:O502 A500 A252:O276 A277 C277 A1:O117 A118 A119:O250 A251" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7890" uniqueCount="7156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7950" uniqueCount="7165">
   <si>
     <t>key</t>
   </si>
@@ -21409,19 +21409,12 @@
     <t>练习例句</t>
   </si>
   <si>
-    <t>enable_fsrs</t>
-  </si>
-  <si>
-    <t>启用遗忘曲线算法</t>
-  </si>
-  <si>
-    <t>enable_fsrs_desc</t>
-  </si>
-  <si>
-    <t>开启后，将使用遗忘曲线(FSRS)算法来决定需要复习的单词,而非固定单词数量; 刚启用时，没有复习词，学习一次之后才有复习词</t>
-  </si>
-  <si>
-    <t>开启后，将使用FSRS算法来决定需要复习的单词,而非固定单词数量</t>
+    <t>fsrs_desc</t>
+  </si>
+  <si>
+    <t>基于“艾宾浩斯遗忘曲线”设计，系统会根据你的记忆情况，自动安排最合适的复习时间。
+不再机械重复，让你用更少时间记住更多单词。
+记得越牢，复习间隔越长；容易忘的内容，会更频繁出现。</t>
   </si>
   <si>
     <t>fsrs_settings</t>
@@ -21430,12 +21423,18 @@
     <t>遗忘曲线设置</t>
   </si>
   <si>
+    <t>不再机械重复，让你用更少时间记住更多单词。</t>
+  </si>
+  <si>
     <t>fsrs_limit_desc</t>
   </si>
   <si>
     <t>在学习过程中对每个单词错误次数进行评级，共有四个评级，Again,Hard,Good,Easy，遗忘曲线算法会使用评级来计算这个单词下一次需要复习的时间。</t>
   </si>
   <si>
+    <t>记得越牢，复习间隔越长；容易忘的内容，会更频繁出现。</t>
+  </si>
+  <si>
     <t>fsrs_easy_limit</t>
   </si>
   <si>
@@ -21509,6 +21508,36 @@
   </si>
   <si>
     <t>最大天数限制</t>
+  </si>
+  <si>
+    <t>export_as_xlsx</t>
+  </si>
+  <si>
+    <t>导出为xlsx文件</t>
+  </si>
+  <si>
+    <t>export_as_json</t>
+  </si>
+  <si>
+    <t>导出为json文件</t>
+  </si>
+  <si>
+    <t>xlsx_template_download</t>
+  </si>
+  <si>
+    <t>xlsx模板下载地址</t>
+  </si>
+  <si>
+    <t>import_xlsx</t>
+  </si>
+  <si>
+    <t>导入xlsx文件</t>
+  </si>
+  <si>
+    <t>import_json</t>
+  </si>
+  <si>
+    <t>导入json文件</t>
   </si>
 </sst>
 </file>
@@ -22135,8 +22164,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -22528,7 +22560,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O526"/>
+  <dimension ref="A1:O530"/>
   <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -46505,756 +46537,944 @@
         <v>7121</v>
       </c>
     </row>
-    <row r="511" spans="1:15">
+    <row r="511" ht="374.4" spans="1:15">
       <c r="A511" t="s">
         <v>7122</v>
       </c>
-      <c r="B511" t="s">
+      <c r="B511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="C511" t="s">
+      <c r="C511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="D511" t="s">
+      <c r="D511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="E511" t="s">
+      <c r="E511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="F511" t="s">
+      <c r="F511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="G511" t="s">
+      <c r="G511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="H511" t="s">
+      <c r="H511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="I511" t="s">
+      <c r="I511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="J511" t="s">
+      <c r="J511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="K511" t="s">
+      <c r="K511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="L511" t="s">
+      <c r="L511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="M511" t="s">
+      <c r="M511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="N511" t="s">
+      <c r="N511" s="1" t="s">
         <v>7123</v>
       </c>
-      <c r="O511" t="s">
+      <c r="O511" s="1" t="s">
         <v>7123</v>
       </c>
     </row>
     <row r="512" spans="1:15">
-      <c r="A512" t="s">
+      <c r="A512" s="2" t="s">
         <v>7124</v>
       </c>
-      <c r="B512" t="s">
+      <c r="B512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="C512" t="s">
+      <c r="C512" s="2" t="s">
+        <v>7126</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="D512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="E512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="F512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="G512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="H512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="I512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="J512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="K512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="L512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="M512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="N512" t="s">
-        <v>7126</v>
-      </c>
-      <c r="O512" t="s">
-        <v>7126</v>
+      <c r="E512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="F512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="G512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="H512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="I512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="J512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="K512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="L512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="M512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="N512" s="2" t="s">
+        <v>7125</v>
+      </c>
+      <c r="O512" s="2" t="s">
+        <v>7125</v>
       </c>
     </row>
     <row r="513" spans="1:15">
-      <c r="A513" s="1" t="s">
+      <c r="A513" s="2" t="s">
         <v>7127</v>
       </c>
-      <c r="B513" s="1" t="s">
+      <c r="B513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="C513" s="1" t="s">
+      <c r="C513" s="3" t="s">
+        <v>7129</v>
+      </c>
+      <c r="D513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="D513" s="1" t="s">
+      <c r="E513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="E513" s="1" t="s">
+      <c r="F513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="F513" s="1" t="s">
+      <c r="G513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="G513" s="1" t="s">
+      <c r="H513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="H513" s="1" t="s">
+      <c r="I513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="I513" s="1" t="s">
+      <c r="J513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="J513" s="1" t="s">
+      <c r="K513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="K513" s="1" t="s">
+      <c r="L513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="L513" s="1" t="s">
+      <c r="M513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="M513" s="1" t="s">
+      <c r="N513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="N513" s="1" t="s">
+      <c r="O513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="O513" s="1" t="s">
-        <v>7128</v>
-      </c>
     </row>
     <row r="514" spans="1:15">
-      <c r="A514" s="1" t="s">
-        <v>7129</v>
+      <c r="A514" s="4" t="s">
+        <v>7130</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="F514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="I514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="K514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="L514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="M514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="N514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
       <c r="O514" s="2" t="s">
-        <v>7130</v>
+        <v>7131</v>
       </c>
     </row>
     <row r="515" spans="1:15">
-      <c r="A515" s="3" t="s">
-        <v>7131</v>
-      </c>
-      <c r="B515" s="1" t="s">
+      <c r="A515" s="2" t="s">
         <v>7132</v>
       </c>
-      <c r="C515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="D515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="E515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="F515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="G515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="H515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="I515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="J515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="K515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="L515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="M515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="N515" s="1" t="s">
-        <v>7132</v>
-      </c>
-      <c r="O515" s="1" t="s">
-        <v>7132</v>
+      <c r="B515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="C515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="E515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="F515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="G515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="H515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="I515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="J515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="K515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="L515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="M515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="N515" s="2" t="s">
+        <v>7133</v>
+      </c>
+      <c r="O515" s="2" t="s">
+        <v>7133</v>
       </c>
     </row>
     <row r="516" spans="1:15">
-      <c r="A516" s="1" t="s">
-        <v>7133</v>
-      </c>
-      <c r="B516" s="1" t="s">
+      <c r="A516" s="2" t="s">
         <v>7134</v>
       </c>
-      <c r="C516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="D516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="E516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="F516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="G516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="H516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="I516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="J516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="K516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="L516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="M516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="N516" s="1" t="s">
-        <v>7134</v>
-      </c>
-      <c r="O516" s="1" t="s">
-        <v>7134</v>
+      <c r="B516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="C516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="E516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="F516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="G516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="H516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="I516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="J516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="K516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="L516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="M516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="N516" s="2" t="s">
+        <v>7135</v>
+      </c>
+      <c r="O516" s="2" t="s">
+        <v>7135</v>
       </c>
     </row>
     <row r="517" spans="1:15">
-      <c r="A517" s="1" t="s">
-        <v>7135</v>
-      </c>
-      <c r="B517" s="1" t="s">
+      <c r="A517" s="2" t="s">
         <v>7136</v>
       </c>
-      <c r="C517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="F517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="G517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="H517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="I517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="J517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="K517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="L517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="M517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="N517" s="1" t="s">
-        <v>7136</v>
-      </c>
-      <c r="O517" s="1" t="s">
-        <v>7136</v>
+      <c r="B517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="D517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="E517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="F517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="G517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="H517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="I517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="J517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="K517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="L517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="M517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="N517" s="2" t="s">
+        <v>7137</v>
+      </c>
+      <c r="O517" s="2" t="s">
+        <v>7137</v>
       </c>
     </row>
     <row r="518" spans="1:15">
-      <c r="A518" s="1" t="s">
-        <v>7137</v>
-      </c>
-      <c r="B518" s="1" t="s">
+      <c r="A518" s="2" t="s">
         <v>7138</v>
       </c>
-      <c r="C518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="D518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="E518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="F518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="G518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="H518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="I518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="J518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="K518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="L518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="M518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="N518" s="1" t="s">
-        <v>7138</v>
-      </c>
-      <c r="O518" s="1" t="s">
-        <v>7138</v>
+      <c r="B518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="E518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="F518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="G518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="H518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="I518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="J518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="K518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="L518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="M518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="N518" s="2" t="s">
+        <v>7139</v>
+      </c>
+      <c r="O518" s="2" t="s">
+        <v>7139</v>
       </c>
     </row>
     <row r="519" spans="1:15">
-      <c r="A519" s="1" t="s">
-        <v>7139</v>
-      </c>
-      <c r="B519" s="1" t="s">
+      <c r="A519" s="2" t="s">
         <v>7140</v>
       </c>
-      <c r="C519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="D519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="E519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="F519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="G519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="H519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="I519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="J519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="K519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="L519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="M519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="N519" s="1" t="s">
-        <v>7140</v>
-      </c>
-      <c r="O519" s="1" t="s">
-        <v>7140</v>
+      <c r="B519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="E519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="H519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="I519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="J519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="K519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="L519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="M519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="N519" s="2" t="s">
+        <v>7141</v>
+      </c>
+      <c r="O519" s="2" t="s">
+        <v>7141</v>
       </c>
     </row>
     <row r="520" spans="1:15">
-      <c r="A520" s="1" t="s">
-        <v>7141</v>
-      </c>
-      <c r="B520" s="1" t="s">
+      <c r="A520" s="2" t="s">
         <v>7142</v>
       </c>
-      <c r="C520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="D520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="E520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="F520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="G520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="H520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="I520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="J520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="K520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="L520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="M520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="N520" s="1" t="s">
-        <v>7142</v>
-      </c>
-      <c r="O520" s="1" t="s">
-        <v>7142</v>
+      <c r="B520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="C520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="E520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="F520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="H520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="I520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="J520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="K520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="L520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="M520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="N520" s="2" t="s">
+        <v>7143</v>
+      </c>
+      <c r="O520" s="2" t="s">
+        <v>7143</v>
       </c>
     </row>
     <row r="521" spans="1:15">
-      <c r="A521" s="1" t="s">
-        <v>7143</v>
-      </c>
-      <c r="B521" s="1" t="s">
+      <c r="A521" s="5" t="s">
         <v>7144</v>
       </c>
-      <c r="C521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="D521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="E521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="F521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="G521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="H521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="I521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="J521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="K521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="L521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="M521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="N521" s="1" t="s">
-        <v>7144</v>
-      </c>
-      <c r="O521" s="1" t="s">
-        <v>7144</v>
+      <c r="B521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="C521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="F521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="G521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="H521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="I521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="J521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="K521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="L521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="M521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="N521" s="2" t="s">
+        <v>7145</v>
+      </c>
+      <c r="O521" s="2" t="s">
+        <v>7145</v>
       </c>
     </row>
     <row r="522" spans="1:15">
-      <c r="A522" s="4" t="s">
-        <v>7145</v>
-      </c>
-      <c r="B522" s="1" t="s">
+      <c r="A522" s="2" t="s">
         <v>7146</v>
       </c>
-      <c r="C522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="D522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="E522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="F522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="G522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="H522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="I522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="J522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="K522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="L522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="M522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="N522" s="1" t="s">
-        <v>7146</v>
-      </c>
-      <c r="O522" s="1" t="s">
-        <v>7146</v>
+      <c r="B522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="C522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="G522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="H522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="I522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="J522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="K522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="L522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="M522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="N522" s="2" t="s">
+        <v>7147</v>
+      </c>
+      <c r="O522" s="2" t="s">
+        <v>7147</v>
       </c>
     </row>
     <row r="523" spans="1:15">
-      <c r="A523" s="1" t="s">
-        <v>7147</v>
-      </c>
-      <c r="B523" s="1" t="s">
+      <c r="A523" s="2" t="s">
         <v>7148</v>
       </c>
-      <c r="C523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="D523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="E523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="F523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="G523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="H523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="I523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="J523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="K523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="L523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="M523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="N523" s="1" t="s">
-        <v>7148</v>
-      </c>
-      <c r="O523" s="1" t="s">
-        <v>7148</v>
+      <c r="B523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="C523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="D523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="G523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="H523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="I523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="J523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="K523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="L523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="M523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="N523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="O523" s="2" t="s">
+        <v>7149</v>
       </c>
     </row>
     <row r="524" spans="1:15">
-      <c r="A524" s="1" t="s">
-        <v>7149</v>
-      </c>
-      <c r="B524" s="1" t="s">
+      <c r="A524" s="2" t="s">
         <v>7150</v>
       </c>
-      <c r="C524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="D524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="E524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="F524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="G524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="H524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="I524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="J524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="K524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="L524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="M524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="N524" s="1" t="s">
-        <v>7150</v>
-      </c>
-      <c r="O524" s="1" t="s">
-        <v>7150</v>
+      <c r="B524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="H524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="I524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="J524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="K524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="L524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="M524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="N524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="O524" s="2" t="s">
+        <v>7151</v>
       </c>
     </row>
     <row r="525" spans="1:15">
-      <c r="A525" s="1" t="s">
-        <v>7151</v>
-      </c>
-      <c r="B525" s="1" t="s">
+      <c r="A525" s="2" t="s">
         <v>7152</v>
       </c>
-      <c r="C525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="D525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="E525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="F525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="G525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="H525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="I525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="J525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="K525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="L525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="M525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="N525" s="1" t="s">
-        <v>7152</v>
-      </c>
-      <c r="O525" s="1" t="s">
-        <v>7152</v>
+      <c r="B525" s="2" t="s">
+        <v>7153</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="E525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="F525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="G525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="H525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="I525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="J525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="K525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="L525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="M525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="N525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="O525" s="2" t="s">
+        <v>7154</v>
       </c>
     </row>
     <row r="526" spans="1:15">
-      <c r="A526" s="1" t="s">
-        <v>7153</v>
-      </c>
-      <c r="B526" s="1" t="s">
-        <v>7154</v>
-      </c>
-      <c r="C526" s="1" t="s">
+      <c r="A526" t="s">
         <v>7155</v>
       </c>
-      <c r="D526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="E526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="F526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="G526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="H526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="I526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="J526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="K526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="L526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="M526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="N526" s="1" t="s">
-        <v>7155</v>
-      </c>
-      <c r="O526" s="1" t="s">
-        <v>7155</v>
+      <c r="B526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="C526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="D526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="E526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="F526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="G526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="H526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="I526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="J526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="K526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="L526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="M526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="N526" t="s">
+        <v>7156</v>
+      </c>
+      <c r="O526" t="s">
+        <v>7156</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15">
+      <c r="A527" t="s">
+        <v>7157</v>
+      </c>
+      <c r="B527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="C527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="D527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="E527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="F527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="G527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="H527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="I527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="J527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="K527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="L527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="M527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="N527" t="s">
+        <v>7158</v>
+      </c>
+      <c r="O527" t="s">
+        <v>7158</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15">
+      <c r="A528" t="s">
+        <v>7159</v>
+      </c>
+      <c r="B528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="C528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="D528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="E528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="F528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="G528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="H528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="I528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="J528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="K528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="L528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="M528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="N528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="O528" t="s">
+        <v>7160</v>
+      </c>
+    </row>
+    <row r="529" spans="1:15">
+      <c r="A529" t="s">
+        <v>7161</v>
+      </c>
+      <c r="B529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="C529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="D529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="E529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="F529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="G529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="H529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="I529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="J529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="K529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="L529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="M529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="N529" t="s">
+        <v>7162</v>
+      </c>
+      <c r="O529" t="s">
+        <v>7162</v>
+      </c>
+    </row>
+    <row r="530" spans="1:15">
+      <c r="A530" t="s">
+        <v>7163</v>
+      </c>
+      <c r="B530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="C530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="D530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="E530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="F530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="G530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="H530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="I530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="J530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="K530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="L530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="M530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="N530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="O530" t="s">
+        <v>7164</v>
       </c>
     </row>
   </sheetData>
@@ -47262,7 +47482,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A277:O447 A448 C448:O448 A449:O467 A469:O497 C118:O118 A502:O508 A501 A499:O500 A498 A250:O274 A275 C275 A1:O117 A118 A119:O248 A249" numberStoredAsText="1"/>
+    <ignoredError sqref="A249 A119:O248 A118 A1:O117 C275 A275 A250:O274 A498 A499:O500 A501 A502:O508 C118:O118 A469:O497 A449:O467 C448:O448 A448 A277:O447" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>